--- a/database_transaksi_rincian.xlsx
+++ b/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,10 +499,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="A2" t="n">
+        <v>7207250142</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -529,10 +527,8 @@
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>4500011424</t>
-        </is>
+      <c r="G2" t="n">
+        <v>4500011424</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -569,6 +565,82 @@
         <v>75538000</v>
       </c>
       <c r="P2" t="inlineStr">
+        <is>
+          <t>Alat Beroperasi Periode 01 sd 31 Juli 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/AB/VII/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4500011424</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1 Jul 2026</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>75538000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>75538000</v>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Alat Beroperasi Periode 01 sd 31 Juli 2026</t>
         </is>
